--- a/resultados/anahy/inventario_externos.xlsx
+++ b/resultados/anahy/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G191"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,7 +484,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:40</t>
+          <t>2026-08-03 00:08:27</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:40</t>
+          <t>2026-08-03 00:08:27</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:40</t>
+          <t>2026-08-03 00:08:27</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:40</t>
+          <t>2026-08-03 00:08:27</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:40</t>
+          <t>2026-08-03 00:08:27</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:40</t>
+          <t>2026-08-03 00:08:27</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:40</t>
+          <t>2026-08-03 00:08:27</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:40</t>
+          <t>2026-08-03 00:08:27</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:40</t>
+          <t>2026-08-03 00:08:27</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:40</t>
+          <t>2026-08-03 00:08:27</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:40</t>
+          <t>2026-08-03 00:08:27</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:40</t>
+          <t>2026-08-03 00:08:27</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -892,17 +892,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://leismunicipais.com.br/prefeitura/pr/anahy</t>
+          <t>https://nfse-anahy.atende.net/autoatendimento/servicos/nfse?redirected=1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>leismunicipais.com.br</t>
+          <t>nfse-anahy.atende.net</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LEIS MUNICIPAISPrefeitura Municipal visa facilitar o acesso e o conhecimento das leis do Município, demonstrando transparência e retidão com o acervo online da legislação. O Portal LeisMunicipais integrado auxilia a identificação de todas as atualizações/alterações das leis - formato Consolidado, Compilado e Versionado.</t>
+          <t>EMISSÃO NFSE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -927,17 +927,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.diariomunicipal.com.br/amp/pesquisar</t>
+          <t>https://nfse-anahy.atende.net/autoatendimento/servicos/nfse</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>www.diariomunicipal.com.br</t>
+          <t>nfse-anahy.atende.net</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DIÁRIO OFICIALDiário Oficial dos Municípios do Paraná</t>
+          <t>DEC SERV PRESTADOS E TOMADOS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -962,15 +962,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Comunicado+de+Leil%C3%A3o+Eletr%C3%B4nico+003%2F2026+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/comunicado-de-leilao-eletronico-0032026</t>
+          <t>https://leismunicipais.com.br/prefeitura/pr/anahy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>leismunicipais.com.br</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LEIS MUNICIPAISPrefeitura Municipal visa facilitar o acesso e o conhecimento das leis do Município, demonstrando transparência e retidão com o acervo online da legislação. O Portal LeisMunicipais integrado auxilia a identificação de todas as atualizações/alterações das leis - formato Consolidado, Compilado e Versionado.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>https://anahy.atende.net/cidadao</t>
@@ -981,7 +985,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -993,15 +997,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/comunicado-de-leilao-eletronico-0032026</t>
+          <t>https://www.diariomunicipal.com.br/amp/pesquisar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>www.diariomunicipal.com.br</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DIÁRIO OFICIALDiário Oficial dos Municípios do Paraná</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>https://anahy.atende.net/cidadao</t>
@@ -1012,7 +1020,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1032,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/comunicado-de-leilao-eletronico-0032026</t>
+          <t>https://api.whatsapp.com/send?text=Comunicado+de+Leil%C3%A3o+Eletr%C3%B4nico+003%2F2026+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/comunicado-de-leilao-eletronico-0032026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1043,7 +1051,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1063,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Munic%C3%ADpio+de+Anahy+realiza+Teste+Seletivo+para+Professor+20h+-+CR+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/municipio-de-anahy-realiza-teste-seletivo-para-professor-20h-cr</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/comunicado-de-leilao-eletronico-0032026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1074,7 +1082,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1094,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/municipio-de-anahy-realiza-teste-seletivo-para-professor-20h-cr</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/comunicado-de-leilao-eletronico-0032026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1105,7 +1113,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1125,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/municipio-de-anahy-realiza-teste-seletivo-para-professor-20h-cr</t>
+          <t>https://api.whatsapp.com/send?text=Munic%C3%ADpio+de+Anahy+realiza+Teste+Seletivo+para+Professor+20h+-+CR+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/municipio-de-anahy-realiza-teste-seletivo-para-professor-20h-cr</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1136,7 +1144,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1156,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=XIV+Confer%C3%AAncia+Municipal+de+Sa%C3%BAde+de+Anahy%3A+Participe+da+constru%C3%A7%C3%A3o+das+pol%C3%ADticas+p%C3%BAblicas+de+sa%C3%BAde+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/xiv-conferencia-municipal-de-saude-de-anahy-participe-da-construcao-das-politicas-publicas-de-saude</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/municipio-de-anahy-realiza-teste-seletivo-para-professor-20h-cr</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1167,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1187,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/xiv-conferencia-municipal-de-saude-de-anahy-participe-da-construcao-das-politicas-publicas-de-saude</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/municipio-de-anahy-realiza-teste-seletivo-para-professor-20h-cr</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1198,7 +1206,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1218,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/xiv-conferencia-municipal-de-saude-de-anahy-participe-da-construcao-das-politicas-publicas-de-saude</t>
+          <t>https://api.whatsapp.com/send?text=XIV+Confer%C3%AAncia+Municipal+de+Sa%C3%BAde+de+Anahy%3A+Participe+da+constru%C3%A7%C3%A3o+das+pol%C3%ADticas+p%C3%BAblicas+de+sa%C3%BAde+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/xiv-conferencia-municipal-de-saude-de-anahy-participe-da-construcao-das-politicas-publicas-de-saude</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1229,7 +1237,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1249,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Novembro+Azul%3A+A%C3%A7%C3%B5es+do+Departamento+de+Sa%C3%BAde+na+Cl%C3%ADnica+da+Fam%C3%ADlia+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/novembro-azul-acoes-do-departamento-de-saude-na-clinica-da-familia</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/xiv-conferencia-municipal-de-saude-de-anahy-participe-da-construcao-das-politicas-publicas-de-saude</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1260,7 +1268,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/novembro-azul-acoes-do-departamento-de-saude-na-clinica-da-familia</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/xiv-conferencia-municipal-de-saude-de-anahy-participe-da-construcao-das-politicas-publicas-de-saude</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1291,7 +1299,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1311,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/novembro-azul-acoes-do-departamento-de-saude-na-clinica-da-familia</t>
+          <t>https://api.whatsapp.com/send?text=Novembro+Azul%3A+A%C3%A7%C3%B5es+do+Departamento+de+Sa%C3%BAde+na+Cl%C3%ADnica+da+Fam%C3%ADlia+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/novembro-azul-acoes-do-departamento-de-saude-na-clinica-da-familia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1322,7 +1330,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1342,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=COMUNICADO+%C3%80+POPULA%C3%87%C3%83O+-+Outubro+Rosa+-+Cuidados+com+a+Sa%C3%BAde+da+Mulher+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/comunicado-a-populacao-outubro-rosa-cuidados-com-a-saude-da-mulher</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/novembro-azul-acoes-do-departamento-de-saude-na-clinica-da-familia</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1353,7 +1361,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1373,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/comunicado-a-populacao-outubro-rosa-cuidados-com-a-saude-da-mulher</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/novembro-azul-acoes-do-departamento-de-saude-na-clinica-da-familia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1384,7 +1392,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1404,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/comunicado-a-populacao-outubro-rosa-cuidados-com-a-saude-da-mulher</t>
+          <t>https://api.whatsapp.com/send?text=COMUNICADO+%C3%80+POPULA%C3%87%C3%83O+-+Outubro+Rosa+-+Cuidados+com+a+Sa%C3%BAde+da+Mulher+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/comunicado-a-populacao-outubro-rosa-cuidados-com-a-saude-da-mulher</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1415,7 +1423,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1435,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Sua+voz+na+cultura+de+Anahy%3A+participe+da+escuta+p%C3%BAblica+da+Lei+Aldir+Blanc%21+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/sua-voz-na-cultura-de-anahy-participe-da-escuta-publica-da-lei-aldir-blanc</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/comunicado-a-populacao-outubro-rosa-cuidados-com-a-saude-da-mulher</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1446,7 +1454,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1466,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/sua-voz-na-cultura-de-anahy-participe-da-escuta-publica-da-lei-aldir-blanc</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/comunicado-a-populacao-outubro-rosa-cuidados-com-a-saude-da-mulher</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1477,7 +1485,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1497,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/sua-voz-na-cultura-de-anahy-participe-da-escuta-publica-da-lei-aldir-blanc</t>
+          <t>https://api.whatsapp.com/send?text=Sua+voz+na+cultura+de+Anahy%3A+participe+da+escuta+p%C3%BAblica+da+Lei+Aldir+Blanc%21+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/sua-voz-na-cultura-de-anahy-participe-da-escuta-publica-da-lei-aldir-blanc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1508,7 +1516,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1528,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Confer%C3%AAncia+Municipal+de+Assist%C3%AAncia+Social+celebra+20+anos+do+SUAS+em+Anahy+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/conferencia-municipal-de-assistencia-social-celebra-20-anos-do-suas-em-anahy</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/sua-voz-na-cultura-de-anahy-participe-da-escuta-publica-da-lei-aldir-blanc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1539,7 +1547,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1559,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/conferencia-municipal-de-assistencia-social-celebra-20-anos-do-suas-em-anahy</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/sua-voz-na-cultura-de-anahy-participe-da-escuta-publica-da-lei-aldir-blanc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1570,7 +1578,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1590,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/conferencia-municipal-de-assistencia-social-celebra-20-anos-do-suas-em-anahy</t>
+          <t>https://api.whatsapp.com/send?text=Confer%C3%AAncia+Municipal+de+Assist%C3%AAncia+Social+celebra+20+anos+do+SUAS+em+Anahy+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/conferencia-municipal-de-assistencia-social-celebra-20-anos-do-suas-em-anahy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1601,7 +1609,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1621,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Programa+Compra+Direta%3A+apoio+a+fam%C3%ADlias+em+situa%C3%A7%C3%A3o+de+vulnerabilidade+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/programa-compra-direta-apoio-a-familias-em-situacao-de-vulnerabilidade</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/conferencia-municipal-de-assistencia-social-celebra-20-anos-do-suas-em-anahy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1632,7 +1640,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1652,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/programa-compra-direta-apoio-a-familias-em-situacao-de-vulnerabilidade</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/conferencia-municipal-de-assistencia-social-celebra-20-anos-do-suas-em-anahy</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1663,7 +1671,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1683,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/programa-compra-direta-apoio-a-familias-em-situacao-de-vulnerabilidade</t>
+          <t>https://api.whatsapp.com/send?text=Programa+Compra+Direta%3A+apoio+a+fam%C3%ADlias+em+situa%C3%A7%C3%A3o+de+vulnerabilidade+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/programa-compra-direta-apoio-a-familias-em-situacao-de-vulnerabilidade</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1694,7 +1702,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1714,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Prefeito+Arilson+Batista+solicita+recep%C3%A7%C3%A3o+de+jornalista+Wilson+Riedlinger%3B+secret%C3%A1rio-geral+Carlos+Reis+recebe+fundador...+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-solicita-recepcao-de-jornalista-wilson-riedlinger-secretariogeral-carlos-reis-recebe-fundador-do-hospital-uopeccan</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/programa-compra-direta-apoio-a-familias-em-situacao-de-vulnerabilidade</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1725,7 +1733,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1745,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-solicita-recepcao-de-jornalista-wilson-riedlinger-secretariogeral-carlos-reis-recebe-fundador-do-hospital-uopeccan</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/programa-compra-direta-apoio-a-familias-em-situacao-de-vulnerabilidade</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1756,7 +1764,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1776,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-solicita-recepcao-de-jornalista-wilson-riedlinger-secretariogeral-carlos-reis-recebe-fundador-do-hospital-uopeccan</t>
+          <t>https://api.whatsapp.com/send?text=Prefeito+Arilson+Batista+solicita+recep%C3%A7%C3%A3o+de+jornalista+Wilson+Riedlinger%3B+secret%C3%A1rio-geral+Carlos+Reis+recebe+fundador...+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-solicita-recepcao-de-jornalista-wilson-riedlinger-secretariogeral-carlos-reis-recebe-fundador-do-hospital-uopeccan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1787,7 +1795,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1807,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Departamento+de+A%C3%A7%C3%A3o+Social+e+Governo+Municipal+celebram+o+Dia+dos+Av%C3%B3s+com+almo%C3%A7o+especial+para+o+Clube+da+Melhor+Idade+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/departamento-de-acao-social-e-governo-municipal-celebram-o-dia-dos-avos-com-almoco-especial-para-o-clube-da-melhor-idade</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-solicita-recepcao-de-jornalista-wilson-riedlinger-secretariogeral-carlos-reis-recebe-fundador-do-hospital-uopeccan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1818,7 +1826,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1830,12 +1838,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/departamento-de-acao-social-e-governo-municipal-celebram-o-dia-dos-avos-com-almoco-especial-para-o-clube-da-melhor-idade</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-solicita-recepcao-de-jornalista-wilson-riedlinger-secretariogeral-carlos-reis-recebe-fundador-do-hospital-uopeccan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1849,7 +1857,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1869,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/departamento-de-acao-social-e-governo-municipal-celebram-o-dia-dos-avos-com-almoco-especial-para-o-clube-da-melhor-idade</t>
+          <t>https://api.whatsapp.com/send?text=Departamento+de+A%C3%A7%C3%A3o+Social+e+Governo+Municipal+celebram+o+Dia+dos+Av%C3%B3s+com+almo%C3%A7o+especial+para+o+Clube+da+Melhor+Idade+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/departamento-de-acao-social-e-governo-municipal-celebram-o-dia-dos-avos-com-almoco-especial-para-o-clube-da-melhor-idade</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1880,7 +1888,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1900,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Anahy+e+Corb%C3%A9lia+avan%C3%A7am+no+projeto+de+pavimenta%C3%A7%C3%A3o+da+estrada+TIMBURI+em+parceria+com+a+COPACOL+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/anahy-e-corbelia-avancam-no-projeto-de-pavimentacao-da-estrada-timburi-em-parceria-com-a-copacol</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/departamento-de-acao-social-e-governo-municipal-celebram-o-dia-dos-avos-com-almoco-especial-para-o-clube-da-melhor-idade</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1911,7 +1919,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1923,12 +1931,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/anahy-e-corbelia-avancam-no-projeto-de-pavimentacao-da-estrada-timburi-em-parceria-com-a-copacol</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/departamento-de-acao-social-e-governo-municipal-celebram-o-dia-dos-avos-com-almoco-especial-para-o-clube-da-melhor-idade</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1942,7 +1950,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1962,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/anahy-e-corbelia-avancam-no-projeto-de-pavimentacao-da-estrada-timburi-em-parceria-com-a-copacol</t>
+          <t>https://api.whatsapp.com/send?text=Anahy+e+Corb%C3%A9lia+avan%C3%A7am+no+projeto+de+pavimenta%C3%A7%C3%A3o+da+estrada+TIMBURI+em+parceria+com+a+COPACOL+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/anahy-e-corbelia-avancam-no-projeto-de-pavimentacao-da-estrada-timburi-em-parceria-com-a-copacol</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1973,7 +1981,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1993,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Anahy+marca+presen%C3%A7a+na+5%C2%AA+Confer%C3%AAncia+Estadual+de+Pol%C3%ADticas+para+Mulheres+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/anahy-marca-presenca-na-5-conferencia-estadual-de-politicas-para-mulheres</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/anahy-e-corbelia-avancam-no-projeto-de-pavimentacao-da-estrada-timburi-em-parceria-com-a-copacol</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -2004,7 +2012,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2024,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/anahy-marca-presenca-na-5-conferencia-estadual-de-politicas-para-mulheres</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/anahy-e-corbelia-avancam-no-projeto-de-pavimentacao-da-estrada-timburi-em-parceria-com-a-copacol</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -2035,7 +2043,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2055,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/anahy-marca-presenca-na-5-conferencia-estadual-de-politicas-para-mulheres</t>
+          <t>https://api.whatsapp.com/send?text=Anahy+marca+presen%C3%A7a+na+5%C2%AA+Confer%C3%AAncia+Estadual+de+Pol%C3%ADticas+para+Mulheres+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/anahy-marca-presenca-na-5-conferencia-estadual-de-politicas-para-mulheres</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2066,7 +2074,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2086,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Anahy+garante+conforto+e+uniformidade%3A+t%C3%AAnis+complementam+uniformes+escolares+e+ber%C3%A7%C3%A1rio+recebe+carrinhos+de+beb%C3%AA+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/anahy-garante-conforto-e-uniformidade-tenis-complementam-uniformes-escolares-e-bercario-recebe-carrinhos-de-bebe</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/anahy-marca-presenca-na-5-conferencia-estadual-de-politicas-para-mulheres</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -2097,7 +2105,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2109,12 +2117,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/anahy-garante-conforto-e-uniformidade-tenis-complementam-uniformes-escolares-e-bercario-recebe-carrinhos-de-bebe</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/anahy-marca-presenca-na-5-conferencia-estadual-de-politicas-para-mulheres</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2128,7 +2136,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2148,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/anahy-garante-conforto-e-uniformidade-tenis-complementam-uniformes-escolares-e-bercario-recebe-carrinhos-de-bebe</t>
+          <t>https://api.whatsapp.com/send?text=Anahy+garante+conforto+e+uniformidade%3A+t%C3%AAnis+complementam+uniformes+escolares+e+ber%C3%A7%C3%A1rio+recebe+carrinhos+de+beb%C3%AA+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/anahy-garante-conforto-e-uniformidade-tenis-complementam-uniformes-escolares-e-bercario-recebe-carrinhos-de-bebe</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2159,7 +2167,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2179,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Agradecimento+aos+artistas+locais+que+participaram+da+Segunda+Etapa+Regional+da+FERMOP+em+Cafel%C3%A2ndia+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/agradecimento-aos-artistas-locais-que-participaram-da-segunda-etapa-regional-da-fermop-em-cafelandia</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/anahy-garante-conforto-e-uniformidade-tenis-complementam-uniformes-escolares-e-bercario-recebe-carrinhos-de-bebe</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2190,7 +2198,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2210,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/agradecimento-aos-artistas-locais-que-participaram-da-segunda-etapa-regional-da-fermop-em-cafelandia</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/anahy-garante-conforto-e-uniformidade-tenis-complementam-uniformes-escolares-e-bercario-recebe-carrinhos-de-bebe</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -2221,7 +2229,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2241,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/agradecimento-aos-artistas-locais-que-participaram-da-segunda-etapa-regional-da-fermop-em-cafelandia</t>
+          <t>https://api.whatsapp.com/send?text=Agradecimento+aos+artistas+locais+que+participaram+da+Segunda+Etapa+Regional+da+FERMOP+em+Cafel%C3%A2ndia+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/agradecimento-aos-artistas-locais-que-participaram-da-segunda-etapa-regional-da-fermop-em-cafelandia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2252,7 +2260,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2272,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Munic%C3%ADpios+da+Regi%C3%A3o+se+Atualizam+sobre+Nova+Lei+de+Licita%C3%A7%C3%B5es+em+Curso+Realizado+em+Corb%C3%A9lia-PR+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/municipios-da-regiao-se-atualizam-sobre-nova-lei-de-licitacoes-em-curso-realizado-em-corbeliapr</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/agradecimento-aos-artistas-locais-que-participaram-da-segunda-etapa-regional-da-fermop-em-cafelandia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -2283,7 +2291,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2303,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/municipios-da-regiao-se-atualizam-sobre-nova-lei-de-licitacoes-em-curso-realizado-em-corbeliapr</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/agradecimento-aos-artistas-locais-que-participaram-da-segunda-etapa-regional-da-fermop-em-cafelandia</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -2314,7 +2322,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2334,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/municipios-da-regiao-se-atualizam-sobre-nova-lei-de-licitacoes-em-curso-realizado-em-corbeliapr</t>
+          <t>https://api.whatsapp.com/send?text=Munic%C3%ADpios+da+Regi%C3%A3o+se+Atualizam+sobre+Nova+Lei+de+Licita%C3%A7%C3%B5es+em+Curso+Realizado+em+Corb%C3%A9lia-PR+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/municipios-da-regiao-se-atualizam-sobre-nova-lei-de-licitacoes-em-curso-realizado-em-corbeliapr</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -2345,7 +2353,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2365,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Ap%C3%B3s+8+anos%2C+Anahy+inaugura+Creas+com+presen%C3%A7a+de+autoridades+estaduais+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/apos-8-anos-anahy-inaugura-creas-com-presenca-de-autoridades-estaduais</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/municipios-da-regiao-se-atualizam-sobre-nova-lei-de-licitacoes-em-curso-realizado-em-corbeliapr</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -2376,7 +2384,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2388,12 +2396,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/apos-8-anos-anahy-inaugura-creas-com-presenca-de-autoridades-estaduais</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/municipios-da-regiao-se-atualizam-sobre-nova-lei-de-licitacoes-em-curso-realizado-em-corbeliapr</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -2407,7 +2415,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2419,12 +2427,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/apos-8-anos-anahy-inaugura-creas-com-presenca-de-autoridades-estaduais</t>
+          <t>https://api.whatsapp.com/send?text=Ap%C3%B3s+8+anos%2C+Anahy+inaugura+Creas+com+presen%C3%A7a+de+autoridades+estaduais+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/apos-8-anos-anahy-inaugura-creas-com-presenca-de-autoridades-estaduais</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2438,7 +2446,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2450,12 +2458,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Pavimenta%C3%A7%C3%A3o+da+estrada+Z%C3%A9+Paran%C3%A1+%C3%A9+conclu%C3%ADda+com+recursos+pr%C3%B3prios+em+Anahy+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/pavimentacao-da-estrada-ze-parana-e-concluida-com-recursos-proprios-em-anahy</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/apos-8-anos-anahy-inaugura-creas-com-presenca-de-autoridades-estaduais</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2469,7 +2477,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2481,12 +2489,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/pavimentacao-da-estrada-ze-parana-e-concluida-com-recursos-proprios-em-anahy</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/apos-8-anos-anahy-inaugura-creas-com-presenca-de-autoridades-estaduais</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2500,7 +2508,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2520,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/pavimentacao-da-estrada-ze-parana-e-concluida-com-recursos-proprios-em-anahy</t>
+          <t>https://api.whatsapp.com/send?text=Pavimenta%C3%A7%C3%A3o+da+estrada+Z%C3%A9+Paran%C3%A1+%C3%A9+conclu%C3%ADda+com+recursos+pr%C3%B3prios+em+Anahy+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/pavimentacao-da-estrada-ze-parana-e-concluida-com-recursos-proprios-em-anahy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2531,7 +2539,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2551,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Nova+sede+do+CREAS%3A+Um+marco+de+conquista+e+esperan%C3%A7a+para+o+munic%C3%ADpio+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/nova-sede-do-creas-um-marco-de-conquista-e-esperanca-para-o-municipio</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/pavimentacao-da-estrada-ze-parana-e-concluida-com-recursos-proprios-em-anahy</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2562,7 +2570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2574,12 +2582,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/nova-sede-do-creas-um-marco-de-conquista-e-esperanca-para-o-municipio</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/pavimentacao-da-estrada-ze-parana-e-concluida-com-recursos-proprios-em-anahy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2593,7 +2601,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2605,12 +2613,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/nova-sede-do-creas-um-marco-de-conquista-e-esperanca-para-o-municipio</t>
+          <t>https://api.whatsapp.com/send?text=Nova+sede+do+CREAS%3A+Um+marco+de+conquista+e+esperan%C3%A7a+para+o+munic%C3%ADpio+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/nova-sede-do-creas-um-marco-de-conquista-e-esperanca-para-o-municipio</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2624,7 +2632,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2636,12 +2644,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Solenidade+de+Entrega+das+Obras+de+Revitaliza%C3%A7%C3%A3o+do+Gin%C3%A1sio+de+Esportes+M%C3%A1rcio+Alex+Bosi+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/solenidade-de-entrega-das-obras-de-revitalizacao-do-ginasio-de-esportes-marcio-alex-bosi</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/nova-sede-do-creas-um-marco-de-conquista-e-esperanca-para-o-municipio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -2655,7 +2663,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2675,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/solenidade-de-entrega-das-obras-de-revitalizacao-do-ginasio-de-esportes-marcio-alex-bosi</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/nova-sede-do-creas-um-marco-de-conquista-e-esperanca-para-o-municipio</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -2686,7 +2694,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2698,12 +2706,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/solenidade-de-entrega-das-obras-de-revitalizacao-do-ginasio-de-esportes-marcio-alex-bosi</t>
+          <t>https://api.whatsapp.com/send?text=Solenidade+de+Entrega+das+Obras+de+Revitaliza%C3%A7%C3%A3o+do+Gin%C3%A1sio+de+Esportes+M%C3%A1rcio+Alex+Bosi+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/solenidade-de-entrega-das-obras-de-revitalizacao-do-ginasio-de-esportes-marcio-alex-bosi</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -2717,7 +2725,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2737,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Prefeito+Arilson+Batista+e+vereadores+buscam+recursos+para+o+munic%C3%ADpio+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-e-vereadores-buscam-recursos-para-o-municipio</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/solenidade-de-entrega-das-obras-de-revitalizacao-do-ginasio-de-esportes-marcio-alex-bosi</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2748,7 +2756,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2760,12 +2768,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-e-vereadores-buscam-recursos-para-o-municipio</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/solenidade-de-entrega-das-obras-de-revitalizacao-do-ginasio-de-esportes-marcio-alex-bosi</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2779,7 +2787,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2799,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-e-vereadores-buscam-recursos-para-o-municipio</t>
+          <t>https://api.whatsapp.com/send?text=Prefeito+Arilson+Batista+e+vereadores+buscam+recursos+para+o+munic%C3%ADpio+%7C+MUNICIPIO+DE+ANAHY%3A+https://anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-e-vereadores-buscam-recursos-para-o-municipio</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2810,7 +2818,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2830,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/dupla-sertaneja-irmaos-freitas-anahy</t>
+          <t>https://twitter.com/intent/tweet?url=https://anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-e-vereadores-buscam-recursos-para-o-municipio</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2841,7 +2849,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2861,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=/cidadao/video/dupla-sertaneja-irmaos-freitas-anahy</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=https://anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-e-vereadores-buscam-recursos-para-o-municipio</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2872,7 +2880,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2884,12 +2892,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/dupla-sertaneja-irmaos-freitas-anahy</t>
+          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/dupla-sertaneja-irmaos-freitas-anahy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2903,7 +2911,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2915,12 +2923,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/anahy-imagens-aereas-noturnas</t>
+          <t>https://twitter.com/intent/tweet?url=/cidadao/video/dupla-sertaneja-irmaos-freitas-anahy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2934,7 +2942,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2954,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=/cidadao/video/anahy-imagens-aereas-noturnas</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/dupla-sertaneja-irmaos-freitas-anahy</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -2965,7 +2973,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -2977,12 +2985,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/anahy-imagens-aereas-noturnas</t>
+          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/anahy-imagens-aereas-noturnas</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2996,7 +3004,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3016,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/anahy-imagens-aereas</t>
+          <t>https://twitter.com/intent/tweet?url=/cidadao/video/anahy-imagens-aereas-noturnas</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -3027,7 +3035,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3039,12 +3047,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=/cidadao/video/anahy-imagens-aereas</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/anahy-imagens-aereas-noturnas</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -3058,7 +3066,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3070,12 +3078,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/anahy-imagens-aereas</t>
+          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/anahy-imagens-aereas</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -3089,7 +3097,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3101,12 +3109,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/cascalhamento-da-estrada-maua</t>
+          <t>https://twitter.com/intent/tweet?url=/cidadao/video/anahy-imagens-aereas</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -3120,7 +3128,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3140,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=/cidadao/video/cascalhamento-da-estrada-maua</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/anahy-imagens-aereas</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -3151,7 +3159,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3163,12 +3171,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/cascalhamento-da-estrada-maua</t>
+          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/cascalhamento-da-estrada-maua</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -3182,7 +3190,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3202,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/prefeito-de-anahy-carlos-antonio-reis-fala-em-entrevista-ao-jornal-primeira-hora-sobre-as-constantes-quedas-de-energia-nos-municipios-do-oeste-do-parana</t>
+          <t>https://twitter.com/intent/tweet?url=/cidadao/video/cascalhamento-da-estrada-maua</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -3213,7 +3221,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3225,12 +3233,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=/cidadao/video/prefeito-de-anahy-carlos-antonio-reis-fala-em-entrevista-ao-jornal-primeira-hora-sobre-as-constantes-quedas-de-energia-nos-municipios-do-oeste-do-parana</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/cascalhamento-da-estrada-maua</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -3244,7 +3252,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3264,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/prefeito-de-anahy-carlos-antonio-reis-fala-em-entrevista-ao-jornal-primeira-hora-sobre-as-constantes-quedas-de-energia-nos-municipios-do-oeste-do-parana</t>
+          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/prefeito-de-anahy-carlos-antonio-reis-fala-em-entrevista-ao-jornal-primeira-hora-sobre-as-constantes-quedas-de-energia-nos-municipios-do-oeste-do-parana</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -3275,7 +3283,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3287,12 +3295,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/governo-municipal-investe-no-bemestar-das-criancas-e-adolescentes-com-transtornos-de-neurodesenvolvimento</t>
+          <t>https://twitter.com/intent/tweet?url=/cidadao/video/prefeito-de-anahy-carlos-antonio-reis-fala-em-entrevista-ao-jornal-primeira-hora-sobre-as-constantes-quedas-de-energia-nos-municipios-do-oeste-do-parana</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -3306,7 +3314,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3318,12 +3326,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=/cidadao/video/governo-municipal-investe-no-bemestar-das-criancas-e-adolescentes-com-transtornos-de-neurodesenvolvimento</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/prefeito-de-anahy-carlos-antonio-reis-fala-em-entrevista-ao-jornal-primeira-hora-sobre-as-constantes-quedas-de-energia-nos-municipios-do-oeste-do-parana</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -3337,7 +3345,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3349,12 +3357,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/governo-municipal-investe-no-bemestar-das-criancas-e-adolescentes-com-transtornos-de-neurodesenvolvimento</t>
+          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/governo-municipal-investe-no-bemestar-das-criancas-e-adolescentes-com-transtornos-de-neurodesenvolvimento</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -3368,7 +3376,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3380,12 +3388,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/hino-municipal-de-anahy-homenagem-aos-31-anos-de-emancipacao-politica-ouca-com-fones-qualidade</t>
+          <t>https://twitter.com/intent/tweet?url=/cidadao/video/governo-municipal-investe-no-bemestar-das-criancas-e-adolescentes-com-transtornos-de-neurodesenvolvimento</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -3399,7 +3407,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3411,12 +3419,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=/cidadao/video/hino-municipal-de-anahy-homenagem-aos-31-anos-de-emancipacao-politica-ouca-com-fones-qualidade</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/governo-municipal-investe-no-bemestar-das-criancas-e-adolescentes-com-transtornos-de-neurodesenvolvimento</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -3430,7 +3438,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3450,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/hino-municipal-de-anahy-homenagem-aos-31-anos-de-emancipacao-politica-ouca-com-fones-qualidade</t>
+          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/hino-municipal-de-anahy-homenagem-aos-31-anos-de-emancipacao-politica-ouca-com-fones-qualidade</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -3461,7 +3469,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3473,12 +3481,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/hino-municipal-de-anahy-pr</t>
+          <t>https://twitter.com/intent/tweet?url=/cidadao/video/hino-municipal-de-anahy-homenagem-aos-31-anos-de-emancipacao-politica-ouca-com-fones-qualidade</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3492,7 +3500,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3504,12 +3512,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=/cidadao/video/hino-municipal-de-anahy-pr</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/hino-municipal-de-anahy-homenagem-aos-31-anos-de-emancipacao-politica-ouca-com-fones-qualidade</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -3523,7 +3531,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3535,12 +3543,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/hino-municipal-de-anahy-pr</t>
+          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/hino-municipal-de-anahy-pr</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -3554,7 +3562,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3574,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/uniao-no-combate-a-dengue-traz-resultados-importantes-para-anahy</t>
+          <t>https://twitter.com/intent/tweet?url=/cidadao/video/hino-municipal-de-anahy-pr</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -3585,7 +3593,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3597,12 +3605,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://twitter.com/intent/tweet?url=/cidadao/video/uniao-no-combate-a-dengue-traz-resultados-importantes-para-anahy</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/hino-municipal-de-anahy-pr</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>twitter.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -3616,7 +3624,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3636,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/uniao-no-combate-a-dengue-traz-resultados-importantes-para-anahy</t>
+          <t>https://api.whatsapp.com/send?text=undefined/cidadao/video/uniao-no-combate-a-dengue-traz-resultados-importantes-para-anahy</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>api.whatsapp.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -3647,7 +3655,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3667,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@AssessoriadeImprensa-v2j</t>
+          <t>https://twitter.com/intent/tweet?url=/cidadao/video/uniao-no-combate-a-dengue-traz-resultados-importantes-para-anahy</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>www.youtube.com</t>
+          <t>twitter.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -3678,7 +3686,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3698,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/municipiodeanahy/</t>
+          <t>https://www.facebook.com/sharer/sharer.php?u=/cidadao/video/uniao-no-combate-a-dengue-traz-resultados-importantes-para-anahy</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>www.instagram.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -3709,7 +3717,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:53</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3721,18 +3729,18 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>http://www.vlibras.gov.br/</t>
+          <t>https://www.youtube.com/@AssessoriadeImprensa-v2j</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>www.vlibras.gov.br</t>
+          <t>www.youtube.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/diariooficial</t>
+          <t>https://anahy.atende.net/cidadao</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3740,7 +3748,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:59</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3752,18 +3760,18 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>http://www.facebook.com/municipiodeanahy</t>
+          <t>https://www.instagram.com/municipiodeanahy/</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>www.instagram.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/diariooficial</t>
+          <t>https://anahy.atende.net/cidadao</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3771,7 +3779,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:59</t>
+          <t>2026-08-03 00:08:43</t>
         </is>
       </c>
     </row>
@@ -3783,12 +3791,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/municipiodeanahy</t>
+          <t>http://www.vlibras.gov.br/</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>www.instagram.com</t>
+          <t>www.vlibras.gov.br</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -3802,7 +3810,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:59</t>
+          <t>2026-08-03 00:09:10</t>
         </is>
       </c>
     </row>
@@ -3814,19 +3822,15 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>http://www.planalto.gov.br/ccivil_03/_ato2011-2014/2011/lei/l12527.htm</t>
+          <t>http://www.facebook.com/municipiodeanahy</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>www.planalto.gov.br</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Conheça a Lei</t>
-        </is>
-      </c>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>https://anahy.atende.net/diariooficial</t>
@@ -3837,7 +3841,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:59</t>
+          <t>2026-08-03 00:09:10</t>
         </is>
       </c>
     </row>
@@ -3849,22 +3853,18 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://servicos.tce.pr.gov.br/TCEPR/Tribunal/Relacon/Obra/ObraConsulta/Contratado/?f=eyJFc2ZlcmFfaWRFc2ZlcmEiOiIwIiwiRXN0cnV0dXJhQWRtaW5pc3RyYWNhb19pZEVzdHJ1dHVyYURlQWRtaW5pc3RyYWNhbyI6IjAiLCJOYXR1cmV6YUp1cmlkaWNhX2lkTmF0dXJlemFKdXJpZGljYSI6IjAiLCJN</t>
+          <t>http://www.instagram.com/municipiodeanahy</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>servicos.tce.pr.gov.br</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Consultas de Obras Públicas no Portal do TCE - PRItem da Transparência</t>
-        </is>
-      </c>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/transparencia/mapa-do-site</t>
+          <t>https://anahy.atende.net/diariooficial</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-30 09:55:06</t>
+          <t>2026-08-03 00:09:10</t>
         </is>
       </c>
     </row>
@@ -3884,30 +3884,30 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j52i9zE6kOQ&amp;t=5s</t>
+          <t>http://www.planalto.gov.br/ccivil_03/_ato2011-2014/2011/lei/l12527.htm</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>www.youtube.com</t>
+          <t>www.planalto.gov.br</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Município de Anahy</t>
+          <t>Conheça a Lei</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/cidadao/pagina/caracteristicas</t>
+          <t>https://anahy.atende.net/diariooficial</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-30 09:59:42</t>
+          <t>2026-08-03 00:09:10</t>
         </is>
       </c>
     </row>
@@ -3919,30 +3919,30 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m1znM2TJTUk&amp;t=31s</t>
+          <t>https://servicos.tce.pr.gov.br/TCEPR/Tribunal/Relacon/Obra/ObraConsulta/Contratado/?f=eyJFc2ZlcmFfaWRFc2ZlcmEiOiIwIiwiRXN0cnV0dXJhQWRtaW5pc3RyYWNhb19pZEVzdHJ1dHVyYURlQWRtaW5pc3RyYWNhbyI6IjAiLCJOYXR1cmV6YUp1cmlkaWNhX2lkTmF0dXJlemFKdXJpZGljYSI6IjAiLCJN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>www.youtube.com</t>
+          <t>servicos.tce.pr.gov.br</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Município de Anahy 2024 - Noturno</t>
+          <t>Consultas de Obras Públicas no Portal do TCE - PR</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/cidadao/pagina/caracteristicas</t>
+          <t>https://anahy.atende.net/transparencia/grupo/obras-publicas</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-30 09:59:42</t>
+          <t>2026-08-03 00:13:09</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=L0i39KZPpb4&amp;ab_channel=AMIGOSQUEVOAM</t>
+          <t>https://www.youtube.com/watch?v=j52i9zE6kOQ&amp;t=5s</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Anahy - Imagem Aérea - PAramotor</t>
+          <t>Município de Anahy</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-30 09:59:42</t>
+          <t>2026-08-03 00:20:20</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iTr67VXOn1Q&amp;t=26s</t>
+          <t>https://www.youtube.com/watch?v=m1znM2TJTUk&amp;t=31s</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Anahy 2017</t>
+          <t>Município de Anahy 2024 - Noturno</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-30 09:59:42</t>
+          <t>2026-08-03 00:20:20</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qwLFzaX7zFk&amp;t=217s</t>
+          <t>https://www.youtube.com/watch?v=L0i39KZPpb4&amp;ab_channel=AMIGOSQUEVOAM</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Imagem Aérea Rio Sapucaí</t>
+          <t>Anahy - Imagem Aérea - PAramotor</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/cidadao/pagina/hidrografia-do-municipio</t>
+          <t>https://anahy.atende.net/cidadao/pagina/caracteristicas</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-30 09:59:48</t>
+          <t>2026-08-03 00:20:20</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9wk4HHiPEk&amp;pp=ygUKaGlubyBhbmFoeQ%3D%3D</t>
+          <t>https://www.youtube.com/watch?v=iTr67VXOn1Q&amp;t=26s</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Hino Municipal</t>
+          <t>Anahy 2017</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/cidadao/pagina/simbolos-municipais</t>
+          <t>https://anahy.atende.net/cidadao/pagina/caracteristicas</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-30 09:59:53</t>
+          <t>2026-08-03 00:20:20</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sAbi1zb46J4&amp;pp=ygUKaGlubyBhbmFoeQ%3D%3D</t>
+          <t>https://www.youtube.com/watch?v=qwLFzaX7zFk&amp;t=217s</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Hino Municipal 2</t>
+          <t>Imagem Aérea Rio Sapucaí</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/cidadao/pagina/simbolos-municipais</t>
+          <t>https://anahy.atende.net/cidadao/pagina/hidrografia-do-municipio</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-30 09:59:53</t>
+          <t>2026-08-03 00:20:34</t>
         </is>
       </c>
     </row>
@@ -4129,22 +4129,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?q=VEREADOR%20LEONARDO%20AP.%20BOBICZ%20594%20Centro%20Anahy%20PR%2085.425-000</t>
+          <t>https://www.youtube.com/watch?v=y9wk4HHiPEk&amp;pp=ygUKaGlubyBhbmFoeQ%3D%3D</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>maps.google.com</t>
+          <t>www.youtube.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Abrir no Mapa</t>
+          <t>Hino Municipal</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/subportal/itr-imposto-territorial-rural</t>
+          <t>https://anahy.atende.net/cidadao/pagina/simbolos-municipais</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:36</t>
+          <t>2026-08-03 00:20:40</t>
         </is>
       </c>
     </row>
@@ -4164,22 +4164,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.bnc.org.br</t>
+          <t>https://www.youtube.com/watch?v=sAbi1zb46J4&amp;pp=ygUKaGlubyBhbmFoeQ%3D%3D</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>www.bnc.org.br</t>
+          <t>www.youtube.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>www.bnc.org.br</t>
+          <t>Hino Municipal 2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/cidadao/noticia/comunicado-de-leilao-eletronico-0032026</t>
+          <t>https://anahy.atende.net/cidadao/pagina/simbolos-municipais</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-30 10:01:34</t>
+          <t>2026-08-03 00:20:40</t>
         </is>
       </c>
     </row>
@@ -4199,17 +4199,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://pncp.gov.br/pncp-api/v1/orgaos/95594800000194/compras/2026/46/arquivos/1</t>
+          <t>https://www.bnc.org.br</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>pncp.gov.br</t>
+          <t>www.bnc.org.br</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://pncp.gov.br/pncp-api/v1/orgaos/95594800000194/compras/2026/46/arquivos/1</t>
+          <t>www.bnc.org.br</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-30 10:01:34</t>
+          <t>2026-08-03 00:23:56</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://pncp.gov.br/app/editais/95594800000194/2026/46</t>
+          <t>https://pncp.gov.br/pncp-api/v1/orgaos/95594800000194/compras/2026/46/arquivos/1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://pncp.gov.br/app/editais/95594800000194/2026/46</t>
+          <t>https://pncp.gov.br/pncp-api/v1/orgaos/95594800000194/compras/2026/46/arquivos/1</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-30 10:01:34</t>
+          <t>2026-08-03 00:23:56</t>
         </is>
       </c>
     </row>
@@ -4269,17 +4269,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1sRTL9Fdtcnc74fZDcA8qC3VZ81Nl-lW1?usp=drive_link</t>
+          <t>https://pncp.gov.br/app/editais/95594800000194/2026/46</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>drive.google.com</t>
+          <t>pncp.gov.br</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1sRTL9Fdtcnc74fZDcA8qC3VZ81Nl-lW1?usp=drive_link</t>
+          <t>https://pncp.gov.br/app/editais/95594800000194/2026/46</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-30 10:01:34</t>
+          <t>2026-08-03 00:23:56</t>
         </is>
       </c>
     </row>
@@ -4304,22 +4304,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://concursos.unioeste.br/concursos/publicacoes/PREFEITURA+MUNICIPAL+DE+ANAHY/136</t>
+          <t>https://drive.google.com/drive/folders/1sRTL9Fdtcnc74fZDcA8qC3VZ81Nl-lW1?usp=drive_link</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>concursos.unioeste.br</t>
+          <t>drive.google.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Clique aqui para fazer sua Inscrição</t>
+          <t>https://drive.google.com/drive/folders/1sRTL9Fdtcnc74fZDcA8qC3VZ81Nl-lW1?usp=drive_link</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/cidadao/noticia/municipio-de-anahy-realiza-teste-seletivo-para-professor-20h-cr</t>
+          <t>https://anahy.atende.net/cidadao/noticia/comunicado-de-leilao-eletronico-0032026</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-30 10:01:39</t>
+          <t>2026-08-03 00:23:56</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-30 10:06:23</t>
+          <t>2026-08-03 00:34:44</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-30 10:06:23</t>
+          <t>2026-08-03 00:34:44</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-30 10:06:23</t>
+          <t>2026-08-03 00:34:44</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-30 10:06:23</t>
+          <t>2026-08-03 00:34:44</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-30 10:06:23</t>
+          <t>2026-08-03 00:34:44</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-30 11:01:19</t>
+          <t>2026-08-03 01:17:03</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-30 11:01:19</t>
+          <t>2026-08-03 01:17:03</t>
         </is>
       </c>
     </row>
@@ -4584,26 +4584,30 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://seal.digicert.com/seals/popup/?tag=KiuKJJzi&amp;url=nfse-anahy.atende.net&amp;lang=pt&amp;cbr=1728501212766</t>
+          <t>https://nfse-anahy.atende.net/autoatendimento/servicos/acesso-ao-sistema-fiscal/detalhar/1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>seal.digicert.com</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>nfse-anahy.atende.net</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Acessar</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://nfse-anahy.atende.net/autoatendimento/servicos/recuperacao-de-senha-de-acesso/detalhar/1</t>
+          <t>https://anahy.atende.net/autoatendimento/servicos/acesso-ao-sistema-fiscal?perfil=false_false</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-30 11:02:05</t>
+          <t>2026-08-03 01:30:54</t>
         </is>
       </c>
     </row>
@@ -4615,1855 +4619,30 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://api.whatsapp.com/send?text=Comunicado+de+Leil%C3%A3o+Eletr%C3%B4nico+003%2F2026+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/comunicado-de-leilao-eletronico-0032026</t>
+          <t>https://maps.google.com/?q=VEREADOR%20LEONARDO%20AP.%20BOBICZ%20594%20Centro%20Anahy%20PR%2085.425-000</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>maps.google.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Abrir no Mapa</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
+          <t>https://anahy.atende.net/subportal/itr-imposto-territorial-rural</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/comunicado-de-leilao-eletronico-0032026</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F133" t="n">
-        <v>6</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/comunicado-de-leilao-eletronico-0032026</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F134" t="n">
-        <v>6</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Munic%C3%ADpio+de+Anahy+realiza+Teste+Seletivo+para+Professor+20h+-+CR+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/municipio-de-anahy-realiza-teste-seletivo-para-professor-20h-cr</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F135" t="n">
-        <v>6</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/municipio-de-anahy-realiza-teste-seletivo-para-professor-20h-cr</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F136" t="n">
-        <v>6</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/municipio-de-anahy-realiza-teste-seletivo-para-professor-20h-cr</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F137" t="n">
-        <v>6</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=XIV+Confer%C3%AAncia+Municipal+de+Sa%C3%BAde+de+Anahy%3A+Participe+da+constru%C3%A7%C3%A3o+das+pol%C3%ADticas+p%C3%BAblicas+de+sa%C3%BAde+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/xiv-conferencia-municipal-de-saude-de-anahy-participe-da-construcao-das-politicas-publicas-de-saude</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F138" t="n">
-        <v>6</v>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/xiv-conferencia-municipal-de-saude-de-anahy-participe-da-construcao-das-politicas-publicas-de-saude</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F139" t="n">
-        <v>6</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/xiv-conferencia-municipal-de-saude-de-anahy-participe-da-construcao-das-politicas-publicas-de-saude</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F140" t="n">
-        <v>6</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Novembro+Azul%3A+A%C3%A7%C3%B5es+do+Departamento+de+Sa%C3%BAde+na+Cl%C3%ADnica+da+Fam%C3%ADlia+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/novembro-azul-acoes-do-departamento-de-saude-na-clinica-da-familia</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F141" t="n">
-        <v>6</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/novembro-azul-acoes-do-departamento-de-saude-na-clinica-da-familia</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F142" t="n">
-        <v>6</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/novembro-azul-acoes-do-departamento-de-saude-na-clinica-da-familia</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F143" t="n">
-        <v>6</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=COMUNICADO+%C3%80+POPULA%C3%87%C3%83O+-+Outubro+Rosa+-+Cuidados+com+a+Sa%C3%BAde+da+Mulher+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/comunicado-a-populacao-outubro-rosa-cuidados-com-a-saude-da-mulher</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F144" t="n">
-        <v>6</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/comunicado-a-populacao-outubro-rosa-cuidados-com-a-saude-da-mulher</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F145" t="n">
-        <v>6</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/comunicado-a-populacao-outubro-rosa-cuidados-com-a-saude-da-mulher</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F146" t="n">
-        <v>6</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Sua+voz+na+cultura+de+Anahy%3A+participe+da+escuta+p%C3%BAblica+da+Lei+Aldir+Blanc%21+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/sua-voz-na-cultura-de-anahy-participe-da-escuta-publica-da-lei-aldir-blanc</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F147" t="n">
-        <v>6</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/sua-voz-na-cultura-de-anahy-participe-da-escuta-publica-da-lei-aldir-blanc</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
-        <v>6</v>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/sua-voz-na-cultura-de-anahy-participe-da-escuta-publica-da-lei-aldir-blanc</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F149" t="n">
-        <v>6</v>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Confer%C3%AAncia+Municipal+de+Assist%C3%AAncia+Social+celebra+20+anos+do+SUAS+em+Anahy+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/conferencia-municipal-de-assistencia-social-celebra-20-anos-do-suas-em-anahy</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
-        <v>6</v>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/conferencia-municipal-de-assistencia-social-celebra-20-anos-do-suas-em-anahy</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F151" t="n">
-        <v>6</v>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/conferencia-municipal-de-assistencia-social-celebra-20-anos-do-suas-em-anahy</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F152" t="n">
-        <v>6</v>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Programa+Compra+Direta%3A+apoio+a+fam%C3%ADlias+em+situa%C3%A7%C3%A3o+de+vulnerabilidade+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/programa-compra-direta-apoio-a-familias-em-situacao-de-vulnerabilidade</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>6</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/programa-compra-direta-apoio-a-familias-em-situacao-de-vulnerabilidade</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F154" t="n">
-        <v>6</v>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/programa-compra-direta-apoio-a-familias-em-situacao-de-vulnerabilidade</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
-        <v>6</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Prefeito+Arilson+Batista+solicita+recep%C3%A7%C3%A3o+de+jornalista+Wilson+Riedlinger%3B+secret%C3%A1rio-geral+Carlos+Reis+recebe+fundador...+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-solicita-recepcao-de-jornalista-wilson-riedlinger-secretariogeral-carlos-reis-recebe-fundador-do-hospital-uopeccan</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>6</v>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-solicita-recepcao-de-jornalista-wilson-riedlinger-secretariogeral-carlos-reis-recebe-fundador-do-hospital-uopeccan</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>6</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-solicita-recepcao-de-jornalista-wilson-riedlinger-secretariogeral-carlos-reis-recebe-fundador-do-hospital-uopeccan</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F158" t="n">
-        <v>6</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Departamento+de+A%C3%A7%C3%A3o+Social+e+Governo+Municipal+celebram+o+Dia+dos+Av%C3%B3s+com+almo%C3%A7o+especial+para+o+Clube+da+Melhor+Idade+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/departamento-de-acao-social-e-governo-municipal-celebram-o-dia-dos-avos-com-almoco-especial-para-o-clube-da-melhor-idade</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F159" t="n">
-        <v>6</v>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/departamento-de-acao-social-e-governo-municipal-celebram-o-dia-dos-avos-com-almoco-especial-para-o-clube-da-melhor-idade</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F160" t="n">
-        <v>6</v>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/departamento-de-acao-social-e-governo-municipal-celebram-o-dia-dos-avos-com-almoco-especial-para-o-clube-da-melhor-idade</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F161" t="n">
-        <v>6</v>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Anahy+e+Corb%C3%A9lia+avan%C3%A7am+no+projeto+de+pavimenta%C3%A7%C3%A3o+da+estrada+TIMBURI+em+parceria+com+a+COPACOL+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/anahy-e-corbelia-avancam-no-projeto-de-pavimentacao-da-estrada-timburi-em-parceria-com-a-copacol</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F162" t="n">
-        <v>6</v>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/anahy-e-corbelia-avancam-no-projeto-de-pavimentacao-da-estrada-timburi-em-parceria-com-a-copacol</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F163" t="n">
-        <v>6</v>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/anahy-e-corbelia-avancam-no-projeto-de-pavimentacao-da-estrada-timburi-em-parceria-com-a-copacol</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F164" t="n">
-        <v>6</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Anahy+marca+presen%C3%A7a+na+5%C2%AA+Confer%C3%AAncia+Estadual+de+Pol%C3%ADticas+para+Mulheres+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/anahy-marca-presenca-na-5-conferencia-estadual-de-politicas-para-mulheres</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F165" t="n">
-        <v>6</v>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/anahy-marca-presenca-na-5-conferencia-estadual-de-politicas-para-mulheres</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F166" t="n">
-        <v>6</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/anahy-marca-presenca-na-5-conferencia-estadual-de-politicas-para-mulheres</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F167" t="n">
-        <v>6</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Anahy+garante+conforto+e+uniformidade%3A+t%C3%AAnis+complementam+uniformes+escolares+e+ber%C3%A7%C3%A1rio+recebe+carrinhos+de+beb%C3%AA+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/anahy-garante-conforto-e-uniformidade-tenis-complementam-uniformes-escolares-e-bercario-recebe-carrinhos-de-bebe</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F168" t="n">
-        <v>6</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/anahy-garante-conforto-e-uniformidade-tenis-complementam-uniformes-escolares-e-bercario-recebe-carrinhos-de-bebe</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F169" t="n">
-        <v>6</v>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/anahy-garante-conforto-e-uniformidade-tenis-complementam-uniformes-escolares-e-bercario-recebe-carrinhos-de-bebe</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F170" t="n">
-        <v>6</v>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Agradecimento+aos+artistas+locais+que+participaram+da+Segunda+Etapa+Regional+da+FERMOP+em+Cafel%C3%A2ndia+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/agradecimento-aos-artistas-locais-que-participaram-da-segunda-etapa-regional-da-fermop-em-cafelandia</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F171" t="n">
-        <v>6</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/agradecimento-aos-artistas-locais-que-participaram-da-segunda-etapa-regional-da-fermop-em-cafelandia</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F172" t="n">
-        <v>6</v>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/agradecimento-aos-artistas-locais-que-participaram-da-segunda-etapa-regional-da-fermop-em-cafelandia</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F173" t="n">
-        <v>6</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Munic%C3%ADpios+da+Regi%C3%A3o+se+Atualizam+sobre+Nova+Lei+de+Licita%C3%A7%C3%B5es+em+Curso+Realizado+em+Corb%C3%A9lia-PR+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/municipios-da-regiao-se-atualizam-sobre-nova-lei-de-licitacoes-em-curso-realizado-em-corbeliapr</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F174" t="n">
-        <v>6</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/municipios-da-regiao-se-atualizam-sobre-nova-lei-de-licitacoes-em-curso-realizado-em-corbeliapr</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F175" t="n">
-        <v>6</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/municipios-da-regiao-se-atualizam-sobre-nova-lei-de-licitacoes-em-curso-realizado-em-corbeliapr</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F176" t="n">
-        <v>6</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Ap%C3%B3s+8+anos%2C+Anahy+inaugura+Creas+com+presen%C3%A7a+de+autoridades+estaduais+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/apos-8-anos-anahy-inaugura-creas-com-presenca-de-autoridades-estaduais</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F177" t="n">
-        <v>6</v>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/apos-8-anos-anahy-inaugura-creas-com-presenca-de-autoridades-estaduais</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F178" t="n">
-        <v>6</v>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/apos-8-anos-anahy-inaugura-creas-com-presenca-de-autoridades-estaduais</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F179" t="n">
-        <v>6</v>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Pavimenta%C3%A7%C3%A3o+da+estrada+Z%C3%A9+Paran%C3%A1+%C3%A9+conclu%C3%ADda+com+recursos+pr%C3%B3prios+em+Anahy+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/pavimentacao-da-estrada-ze-parana-e-concluida-com-recursos-proprios-em-anahy</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F180" t="n">
-        <v>6</v>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/pavimentacao-da-estrada-ze-parana-e-concluida-com-recursos-proprios-em-anahy</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F181" t="n">
-        <v>6</v>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/pavimentacao-da-estrada-ze-parana-e-concluida-com-recursos-proprios-em-anahy</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F182" t="n">
-        <v>6</v>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Nova+sede+do+CREAS%3A+Um+marco+de+conquista+e+esperan%C3%A7a+para+o+munic%C3%ADpio+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/nova-sede-do-creas-um-marco-de-conquista-e-esperanca-para-o-municipio</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F183" t="n">
-        <v>6</v>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/nova-sede-do-creas-um-marco-de-conquista-e-esperanca-para-o-municipio</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F184" t="n">
-        <v>6</v>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/nova-sede-do-creas-um-marco-de-conquista-e-esperanca-para-o-municipio</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F185" t="n">
-        <v>6</v>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Solenidade+de+Entrega+das+Obras+de+Revitaliza%C3%A7%C3%A3o+do+Gin%C3%A1sio+de+Esportes+M%C3%A1rcio+Alex+Bosi+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/solenidade-de-entrega-das-obras-de-revitalizacao-do-ginasio-de-esportes-marcio-alex-bosi</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F186" t="n">
-        <v>6</v>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/solenidade-de-entrega-das-obras-de-revitalizacao-do-ginasio-de-esportes-marcio-alex-bosi</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F187" t="n">
-        <v>6</v>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/solenidade-de-entrega-das-obras-de-revitalizacao-do-ginasio-de-esportes-marcio-alex-bosi</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F188" t="n">
-        <v>6</v>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>https://api.whatsapp.com/send?text=Prefeito+Arilson+Batista+e+vereadores+buscam+recursos+para+o+munic%C3%ADpio+%7C+MUNICIPIO+DE+ANAHY%3A+https://nfse-anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-e-vereadores-buscam-recursos-para-o-municipio</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>api.whatsapp.com</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F189" t="n">
-        <v>6</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>https://twitter.com/intent/tweet?url=https://nfse-anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-e-vereadores-buscam-recursos-para-o-municipio</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>twitter.com</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F190" t="n">
-        <v>6</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/sharer/sharer.php?u=https://nfse-anahy.atende.net/cidadao/noticia/prefeito-arilson-batista-e-vereadores-buscam-recursos-para-o-municipio</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/</t>
-        </is>
-      </c>
-      <c r="F191" t="n">
-        <v>6</v>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:22:55</t>
+          <t>2026-08-03 01:56:30</t>
         </is>
       </c>
     </row>
